--- a/assets/downloads/CotizacionBRYAN RUIZ.xlsx
+++ b/assets/downloads/CotizacionBRYAN RUIZ.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="120">
   <si>
     <t>PRO MUNDO COMEX S.A.C.</t>
   </si>
@@ -167,7 +167,7 @@
     <t>PRECIO UNIT. (SOLES)</t>
   </si>
   <si>
-    <t>TORRE PARA GATOS</t>
+    <t>hola</t>
   </si>
   <si>
     <t>NOTAS:</t>
@@ -426,7 +426,7 @@
     <t>N.Proveedor</t>
   </si>
   <si>
-    <t>haruka</t>
+    <t>chino</t>
   </si>
   <si>
     <t>N° Cajas</t>
@@ -484,6 +484,9 @@
   </si>
   <si>
     <t>ANTIDUMPING</t>
+  </si>
+  <si>
+    <t>=</t>
   </si>
   <si>
     <t>AD VALOREM</t>
@@ -1747,7 +1750,7 @@
         <v>20</v>
       </c>
       <c r="J11" s="85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="85"/>
       <c r="L11" s="85"/>
@@ -3227,9 +3230,7 @@
       <c r="B14" t="s">
         <v>96</v>
       </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
+      <c r="C14"/>
       <c r="D14" t="str">
         <f>SUM(C14:C14)</f>
         <v>0</v>
@@ -3239,9 +3240,7 @@
       <c r="B15" t="s">
         <v>97</v>
       </c>
-      <c r="C15">
-        <v>31.333333333333</v>
-      </c>
+      <c r="C15"/>
       <c r="D15" t="str">
         <f>SUM(C15:C15)</f>
         <v>0</v>
@@ -3256,9 +3255,7 @@
       <c r="B17" t="s">
         <v>99</v>
       </c>
-      <c r="C17">
-        <v>6</v>
-      </c>
+      <c r="C17"/>
       <c r="D17" t="str">
         <f>SUM(C17:C17)</f>
         <v>0</v>
@@ -3368,7 +3365,7 @@
         <v>107</v>
       </c>
       <c r="C31" t="str">
-        <f>-*C17</f>
+        <f>*C17</f>
         <v>0</v>
       </c>
       <c r="D31" t="str">
@@ -3377,17 +3374,16 @@
       </c>
     </row>
     <row r="33" spans="1:26">
-      <c r="C33" s="90" t="str">
-        <f>0</f>
-        <v>0</v>
+      <c r="C33" s="90" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:26">
       <c r="B34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C34" t="str">
-        <f>0*C23</f>
+        <f>*C23</f>
         <v>0</v>
       </c>
       <c r="D34" t="str">
@@ -3397,7 +3393,7 @@
     </row>
     <row r="35" spans="1:26">
       <c r="B35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C35" t="str">
         <f>C23*0.16</f>
@@ -3410,7 +3406,7 @@
     </row>
     <row r="36" spans="1:26">
       <c r="B36" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C36" t="str">
         <f>C23*0.02</f>
@@ -3423,10 +3419,10 @@
     </row>
     <row r="37" spans="1:26">
       <c r="B37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C37" t="str">
-        <f>C23*0.035</f>
+        <f>C23*</f>
         <v>0</v>
       </c>
       <c r="D37" t="str">
@@ -3449,7 +3445,7 @@
     </row>
     <row r="39" spans="1:26">
       <c r="T39" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:26">
@@ -3459,7 +3455,7 @@
     </row>
     <row r="42" spans="1:26">
       <c r="B42" s="87" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C42" s="86"/>
       <c r="D42" s="86"/>
@@ -3488,7 +3484,7 @@
     </row>
     <row r="45" spans="1:26">
       <c r="B45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C45" t="str">
         <f>D45*C19</f>
@@ -3501,7 +3497,7 @@
     </row>
     <row r="48" spans="1:26">
       <c r="B48" s="87" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C48" s="86"/>
       <c r="D48" s="86"/>
@@ -3530,7 +3526,7 @@
     </row>
     <row r="50" spans="1:26">
       <c r="B50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C50" t="s">
         <v>49</v>
@@ -3538,7 +3534,7 @@
     </row>
     <row r="51" spans="1:26">
       <c r="B51" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C51" t="str">
         <f>C21+C31+C38+C45</f>
@@ -3556,7 +3552,7 @@
     </row>
     <row r="53" spans="1:26">
       <c r="B53" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C53" t="str">
         <f>C51/C52</f>
@@ -3565,7 +3561,7 @@
     </row>
     <row r="54" spans="1:26">
       <c r="B54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C54" t="str">
         <f>C53*T40</f>

--- a/assets/downloads/CotizacionBRYAN RUIZ.xlsx
+++ b/assets/downloads/CotizacionBRYAN RUIZ.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId4"/>
@@ -113,9 +113,9 @@
     <t>Hola BRYAN RUIZ 😁 un gusto saludarte!
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
-        ☑️Costo CBM: $11.61864
+        ☑️Costo CBM: $356.4
         ☑️Impuestos: $3679.9
-        ☑️ Total: $3691.51864
+        ☑️ Total: $4036.3
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -2186,7 +2186,7 @@
       <c r="I31" s="49"/>
       <c r="J31" s="49"/>
       <c r="K31" s="14" t="str">
-        <f>'2'!AB7*J11</f>
+        <f>IF('2'!AF7&lt;1, '2'!AF7*J11, '2'!AF7*J11)</f>
         <v>0</v>
       </c>
       <c r="L31" s="9" t="s">

--- a/assets/downloads/CotizacionBRYAN RUIZ.xlsx
+++ b/assets/downloads/CotizacionBRYAN RUIZ.xlsx
@@ -1818,8 +1818,9 @@
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="99">
-        <v>244.5</v>
+      <c r="J11" s="99" t="str">
+        <f>'2'!AB7</f>
+        <v>0</v>
       </c>
       <c r="K11" s="73"/>
       <c r="L11" s="73"/>

--- a/assets/downloads/CotizacionBRYAN RUIZ.xlsx
+++ b/assets/downloads/CotizacionBRYAN RUIZ.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="136">
   <si>
     <t>PRO MUNDO COMEX S.A.C.</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>TELEFONO:</t>
-  </si>
-  <si>
-    <t>929 610 511</t>
   </si>
   <si>
     <t>CLIENTE:</t>
@@ -117,8 +114,8 @@
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
         ☑️Costo CBM: $356.4
-        ☑️Impuestos: $3333.59
-        ☑️ Total: $3689.99
+        ☑️Impuestos: $3679.72
+        ☑️ Total: $4036.12
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -1805,20 +1802,20 @@
       <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>17</v>
+      <c r="C11" s="17">
+        <v>51934958839</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="48" t="s">
         <v>18</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>19</v>
       </c>
       <c r="G11" s="65"/>
       <c r="H11" s="33"/>
       <c r="I11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J11" s="99" t="str">
         <f>'2'!AB7</f>
@@ -1842,7 +1839,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="66"/>
       <c r="D13" s="66"/>
@@ -1853,15 +1850,15 @@
       <c r="I13" s="66"/>
       <c r="J13" s="66"/>
       <c r="K13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="67"/>
       <c r="D14" s="67"/>
@@ -1876,12 +1873,12 @@
         <v>0</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="68"/>
       <c r="D15" s="68"/>
@@ -1896,12 +1893,12 @@
         <v>0</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="B16" s="51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
@@ -1916,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1947,7 +1944,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="69"/>
       <c r="D19" s="69"/>
@@ -1957,18 +1954,18 @@
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
       <c r="J19" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="B20" s="49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" s="49"/>
       <c r="D20" s="49"/>
@@ -1986,15 +1983,15 @@
         <v>0</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="49"/>
       <c r="D21" s="49"/>
@@ -2011,12 +2008,12 @@
         <v>0</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="B22" s="48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="48"/>
       <c r="D22" s="48"/>
@@ -2033,12 +2030,12 @@
         <v>0</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="B23" s="95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="95"/>
       <c r="D23" s="95"/>
@@ -2055,7 +2052,7 @@
     </row>
     <row r="24" spans="1:14">
       <c r="B24" s="51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
@@ -2070,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -2088,7 +2085,7 @@
     </row>
     <row r="26" spans="1:14">
       <c r="B26" s="48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="48"/>
       <c r="D26" s="48"/>
@@ -2098,19 +2095,19 @@
       <c r="H26" s="48"/>
       <c r="I26" s="48"/>
       <c r="J26" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K26" s="15" t="str">
         <f>'2'!AB31</f>
         <v>0</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="B27" s="51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" s="51"/>
       <c r="D27" s="51"/>
@@ -2124,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2139,7 +2136,7 @@
     </row>
     <row r="29" spans="1:14" customHeight="1" ht="15.6">
       <c r="B29" s="52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C29" s="52"/>
       <c r="D29" s="52"/>
@@ -2150,15 +2147,15 @@
       <c r="I29" s="52"/>
       <c r="J29" s="52"/>
       <c r="K29" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="28" t="s">
         <v>22</v>
-      </c>
-      <c r="L29" s="28" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="B30" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30" s="49"/>
       <c r="D30" s="49"/>
@@ -2173,12 +2170,12 @@
         <v>0</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="B31" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C31" s="49"/>
       <c r="D31" s="49"/>
@@ -2193,12 +2190,12 @@
         <v>0</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="B32" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="48"/>
       <c r="D32" s="48"/>
@@ -2213,12 +2210,12 @@
         <v>0</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="B33" s="51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C33" s="51"/>
       <c r="D33" s="51"/>
@@ -2233,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2251,7 +2248,7 @@
     </row>
     <row r="35" spans="1:14">
       <c r="B35" s="59" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="60"/>
       <c r="D35" s="60"/>
@@ -2266,28 +2263,28 @@
     </row>
     <row r="36" spans="1:14">
       <c r="B36" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="56" t="s">
         <v>45</v>
-      </c>
-      <c r="C36" s="56" t="s">
-        <v>46</v>
       </c>
       <c r="D36" s="57"/>
       <c r="E36" s="58"/>
       <c r="F36" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36" s="56" t="s">
         <v>47</v>
-      </c>
-      <c r="G36" s="56" t="s">
-        <v>48</v>
       </c>
       <c r="H36" s="58"/>
       <c r="I36" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J36" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="K36" s="47" t="s">
         <v>49</v>
-      </c>
-      <c r="J36" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="K36" s="47" t="s">
-        <v>50</v>
       </c>
       <c r="L36" s="47"/>
     </row>
@@ -2296,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -2329,7 +2326,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -2362,7 +2359,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -2395,7 +2392,7 @@
         <v>4</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -2428,7 +2425,7 @@
         <v>5</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -2460,7 +2457,7 @@
         <v>6</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -2492,7 +2489,7 @@
         <v>7</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -2524,7 +2521,7 @@
         <v>8</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
@@ -2556,7 +2553,7 @@
         <v>9</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -2588,7 +2585,7 @@
         <v>10</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
@@ -2620,7 +2617,7 @@
         <v>11</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -2652,7 +2649,7 @@
         <v>12</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
@@ -2684,7 +2681,7 @@
         <v>13</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -2716,7 +2713,7 @@
         <v>14</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
@@ -2748,7 +2745,7 @@
         <v>15</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -2780,7 +2777,7 @@
         <v>16</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
@@ -2812,7 +2809,7 @@
         <v>17</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -2844,7 +2841,7 @@
         <v>18</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
@@ -2876,7 +2873,7 @@
         <v>19</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -2908,7 +2905,7 @@
         <v>20</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
@@ -2940,7 +2937,7 @@
         <v>21</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -2972,7 +2969,7 @@
         <v>22</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -3004,7 +3001,7 @@
         <v>23</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
@@ -3036,7 +3033,7 @@
         <v>24</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
@@ -3068,7 +3065,7 @@
         <v>25</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
@@ -3097,7 +3094,7 @@
     </row>
     <row r="62" spans="1:14" customHeight="1" ht="18">
       <c r="B62" s="93" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C62" s="92"/>
       <c r="D62" s="92"/>
@@ -3222,7 +3219,7 @@
     </row>
     <row r="65" spans="1:14" customHeight="1" ht="18">
       <c r="B65" s="64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C65" s="64"/>
       <c r="D65" s="64"/>
@@ -3321,7 +3318,7 @@
       <c r="B70" s="38"/>
       <c r="C70" s="38"/>
       <c r="D70" s="53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E70" s="53"/>
       <c r="F70" s="53"/>
@@ -3339,7 +3336,7 @@
     </row>
     <row r="73" spans="1:14" customHeight="1" ht="21">
       <c r="B73" s="70" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C73" s="70"/>
       <c r="D73" s="70"/>
@@ -3354,7 +3351,7 @@
     </row>
     <row r="75" spans="1:14">
       <c r="B75" s="71" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C75" s="71"/>
       <c r="D75" s="71"/>
@@ -3369,7 +3366,7 @@
     </row>
     <row r="76" spans="1:14">
       <c r="B76" s="71" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C76" s="71"/>
       <c r="D76" s="71"/>
@@ -3384,7 +3381,7 @@
     </row>
     <row r="77" spans="1:14">
       <c r="B77" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C77" s="49"/>
       <c r="D77" s="49"/>
@@ -3399,7 +3396,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="B78" s="71" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C78" s="71"/>
       <c r="D78" s="71"/>
@@ -3414,7 +3411,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="B79" s="71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C79" s="71"/>
       <c r="D79" s="71"/>
@@ -3429,7 +3426,7 @@
     </row>
     <row r="80" spans="1:14">
       <c r="B80" s="49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C80" s="49"/>
       <c r="D80" s="49"/>
@@ -3444,7 +3441,7 @@
     </row>
     <row r="81" spans="1:14">
       <c r="B81" s="71" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C81" s="71"/>
       <c r="D81" s="71"/>
@@ -3459,7 +3456,7 @@
     </row>
     <row r="82" spans="1:14">
       <c r="B82" s="71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C82" s="71"/>
       <c r="D82" s="71"/>
@@ -3474,7 +3471,7 @@
     </row>
     <row r="83" spans="1:14">
       <c r="B83" s="71" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C83" s="71"/>
       <c r="D83" s="71"/>
@@ -3489,7 +3486,7 @@
     </row>
     <row r="84" spans="1:14">
       <c r="B84" s="71" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C84" s="71"/>
       <c r="D84" s="71"/>
@@ -3504,7 +3501,7 @@
     </row>
     <row r="85" spans="1:14">
       <c r="B85" s="71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C85" s="71"/>
       <c r="D85" s="71"/>
@@ -3519,7 +3516,7 @@
     </row>
     <row r="86" spans="1:14">
       <c r="B86" s="71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C86" s="71"/>
       <c r="D86" s="71"/>
@@ -3534,7 +3531,7 @@
     </row>
     <row r="87" spans="1:14">
       <c r="B87" s="71" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C87" s="71"/>
       <c r="D87" s="71"/>
@@ -3549,7 +3546,7 @@
     </row>
     <row r="88" spans="1:14">
       <c r="B88" s="71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C88" s="71"/>
       <c r="D88" s="71"/>
@@ -3564,7 +3561,7 @@
     </row>
     <row r="89" spans="1:14">
       <c r="B89" s="71" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C89" s="71"/>
       <c r="D89" s="71"/>
@@ -3579,7 +3576,7 @@
     </row>
     <row r="90" spans="1:14">
       <c r="B90" s="71" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C90" s="71"/>
       <c r="D90" s="71"/>
@@ -3637,7 +3634,7 @@
     </row>
     <row r="92" spans="1:14">
       <c r="B92" s="67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C92" s="67"/>
       <c r="D92" s="67"/>
@@ -3652,7 +3649,7 @@
     </row>
     <row r="93" spans="1:14">
       <c r="B93" s="71" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C93" s="71"/>
       <c r="D93" s="71"/>
@@ -3667,7 +3664,7 @@
     </row>
     <row r="94" spans="1:14">
       <c r="B94" s="67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C94" s="67"/>
       <c r="D94" s="67"/>
@@ -3682,7 +3679,7 @@
     </row>
     <row r="95" spans="1:14">
       <c r="B95" s="71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C95" s="71"/>
       <c r="D95" s="71"/>
@@ -3697,7 +3694,7 @@
     </row>
     <row r="96" spans="1:14">
       <c r="B96" s="71" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C96" s="71"/>
       <c r="D96" s="71"/>
@@ -3712,7 +3709,7 @@
     </row>
     <row r="97" spans="1:14">
       <c r="B97" s="71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C97" s="71"/>
       <c r="D97" s="71"/>
@@ -3727,7 +3724,7 @@
     </row>
     <row r="98" spans="1:14">
       <c r="B98" s="71" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C98" s="71"/>
       <c r="D98" s="71"/>
@@ -3742,7 +3739,7 @@
     </row>
     <row r="99" spans="1:14">
       <c r="B99" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C99" s="71"/>
       <c r="D99" s="71"/>
@@ -3758,7 +3755,7 @@
     <row r="100" spans="1:14">
       <c r="A100" s="32"/>
       <c r="B100" s="72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C100" s="72"/>
       <c r="D100" s="72"/>
@@ -3774,7 +3771,7 @@
     <row r="101" spans="1:14">
       <c r="A101" s="32"/>
       <c r="B101" s="71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C101" s="71"/>
       <c r="D101" s="71"/>
@@ -3790,7 +3787,7 @@
     <row r="102" spans="1:14">
       <c r="A102" s="32"/>
       <c r="B102" s="72" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C102" s="72"/>
       <c r="D102" s="72"/>
@@ -4128,7 +4125,7 @@
   <sheetData>
     <row r="3" spans="1:32">
       <c r="B3" s="75" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C3" s="74"/>
       <c r="D3" s="74"/>
@@ -4138,90 +4135,90 @@
     </row>
     <row r="5" spans="1:32">
       <c r="B5" s="78" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="80" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="80" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="80" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="80" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="80" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="80" t="s">
+        <v>60</v>
+      </c>
+      <c r="N5" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="O5" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="P5" s="80" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q5" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="R5" s="80" t="s">
+        <v>65</v>
+      </c>
+      <c r="S5" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="T5" s="80" t="s">
+        <v>67</v>
+      </c>
+      <c r="U5" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="V5" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="W5" s="80" t="s">
+        <v>70</v>
+      </c>
+      <c r="X5" s="80" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y5" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z5" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA5" s="80" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB5" s="80" t="s">
         <v>111</v>
-      </c>
-      <c r="C5" s="80" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="80" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="80" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="80" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="80" t="s">
-        <v>55</v>
-      </c>
-      <c r="H5" s="80" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="80" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="80" t="s">
-        <v>58</v>
-      </c>
-      <c r="K5" s="80" t="s">
-        <v>59</v>
-      </c>
-      <c r="L5" s="80" t="s">
-        <v>60</v>
-      </c>
-      <c r="M5" s="80" t="s">
-        <v>61</v>
-      </c>
-      <c r="N5" s="80" t="s">
-        <v>62</v>
-      </c>
-      <c r="O5" s="80" t="s">
-        <v>63</v>
-      </c>
-      <c r="P5" s="80" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q5" s="80" t="s">
-        <v>65</v>
-      </c>
-      <c r="R5" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="S5" s="80" t="s">
-        <v>67</v>
-      </c>
-      <c r="T5" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="U5" s="80" t="s">
-        <v>69</v>
-      </c>
-      <c r="V5" s="80" t="s">
-        <v>70</v>
-      </c>
-      <c r="W5" s="80" t="s">
-        <v>71</v>
-      </c>
-      <c r="X5" s="80" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y5" s="80" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z5" s="80" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA5" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB5" s="80" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:32">
       <c r="B6" s="74" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C6" s="74">
         <v>0</v>
@@ -4302,15 +4299,15 @@
         <v>1.37</v>
       </c>
       <c r="AE6" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF6" s="76" t="s">
         <v>114</v>
-      </c>
-      <c r="AF6" s="76" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="74">
         <v>0</v>
@@ -4388,10 +4385,10 @@
         <v>0</v>
       </c>
       <c r="AB7" s="83">
-        <v>2</v>
+        <v>9.78</v>
       </c>
       <c r="AE7" s="77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF7" s="77">
         <v>300</v>
@@ -4399,7 +4396,7 @@
     </row>
     <row r="8" spans="1:32">
       <c r="B8" s="74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="81">
         <v>16.392307692308</v>
@@ -4480,7 +4477,7 @@
     </row>
     <row r="9" spans="1:32">
       <c r="B9" s="79" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C9" s="81">
         <v>0</v>
@@ -4561,7 +4558,7 @@
     </row>
     <row r="10" spans="1:32">
       <c r="B10" s="74" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C10" s="74">
         <v>65</v>
@@ -4645,7 +4642,7 @@
     </row>
     <row r="11" spans="1:32">
       <c r="B11" s="74" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="81" t="str">
         <f>C8*C10</f>
@@ -4754,7 +4751,7 @@
     </row>
     <row r="12" spans="1:32">
       <c r="B12" s="79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="81" t="str">
         <f>C10*C9</f>
@@ -4863,7 +4860,7 @@
     </row>
     <row r="13" spans="1:32">
       <c r="B13" s="74" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C13" s="84" t="str">
         <f>C11/AB11</f>
@@ -4969,215 +4966,215 @@
     </row>
     <row r="14" spans="1:32">
       <c r="B14" s="74" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="81" t="str">
-        <f>ROUNDUP(AB14*C13,2)</f>
+        <f>AB14*C13</f>
         <v>0</v>
       </c>
       <c r="D14" s="81" t="str">
-        <f>ROUNDUP(AB14*D13,2)</f>
+        <f>AB14*D13</f>
         <v>0</v>
       </c>
       <c r="E14" s="81" t="str">
-        <f>ROUNDUP(AB14*E13,2)</f>
+        <f>AB14*E13</f>
         <v>0</v>
       </c>
       <c r="F14" s="81" t="str">
-        <f>ROUNDUP(AB14*F13,2)</f>
+        <f>AB14*F13</f>
         <v>0</v>
       </c>
       <c r="G14" s="81" t="str">
-        <f>ROUNDUP(AB14*G13,2)</f>
+        <f>AB14*G13</f>
         <v>0</v>
       </c>
       <c r="H14" s="81" t="str">
-        <f>ROUNDUP(AB14*H13,2)</f>
+        <f>AB14*H13</f>
         <v>0</v>
       </c>
       <c r="I14" s="81" t="str">
-        <f>ROUNDUP(AB14*I13,2)</f>
+        <f>AB14*I13</f>
         <v>0</v>
       </c>
       <c r="J14" s="81" t="str">
-        <f>ROUNDUP(AB14*J13,2)</f>
+        <f>AB14*J13</f>
         <v>0</v>
       </c>
       <c r="K14" s="81" t="str">
-        <f>ROUNDUP(AB14*K13,2)</f>
+        <f>AB14*K13</f>
         <v>0</v>
       </c>
       <c r="L14" s="81" t="str">
-        <f>ROUNDUP(AB14*L13,2)</f>
+        <f>AB14*L13</f>
         <v>0</v>
       </c>
       <c r="M14" s="81" t="str">
-        <f>ROUNDUP(AB14*M13,2)</f>
+        <f>AB14*M13</f>
         <v>0</v>
       </c>
       <c r="N14" s="81" t="str">
-        <f>ROUNDUP(AB14*N13,2)</f>
+        <f>AB14*N13</f>
         <v>0</v>
       </c>
       <c r="O14" s="81" t="str">
-        <f>ROUNDUP(AB14*O13,2)</f>
+        <f>AB14*O13</f>
         <v>0</v>
       </c>
       <c r="P14" s="81" t="str">
-        <f>ROUNDUP(AB14*P13,2)</f>
+        <f>AB14*P13</f>
         <v>0</v>
       </c>
       <c r="Q14" s="81" t="str">
-        <f>ROUNDUP(AB14*Q13,2)</f>
+        <f>AB14*Q13</f>
         <v>0</v>
       </c>
       <c r="R14" s="81" t="str">
-        <f>ROUNDUP(AB14*R13,2)</f>
+        <f>AB14*R13</f>
         <v>0</v>
       </c>
       <c r="S14" s="81" t="str">
-        <f>ROUNDUP(AB14*S13,2)</f>
+        <f>AB14*S13</f>
         <v>0</v>
       </c>
       <c r="T14" s="81" t="str">
-        <f>ROUNDUP(AB14*T13,2)</f>
+        <f>AB14*T13</f>
         <v>0</v>
       </c>
       <c r="U14" s="81" t="str">
-        <f>ROUNDUP(AB14*U13,2)</f>
+        <f>AB14*U13</f>
         <v>0</v>
       </c>
       <c r="V14" s="81" t="str">
-        <f>ROUNDUP(AB14*V13,2)</f>
+        <f>AB14*V13</f>
         <v>0</v>
       </c>
       <c r="W14" s="81" t="str">
-        <f>ROUNDUP(AB14*W13,2)</f>
+        <f>AB14*W13</f>
         <v>0</v>
       </c>
       <c r="X14" s="81" t="str">
-        <f>ROUNDUP(AB14*X13,2)</f>
+        <f>AB14*X13</f>
         <v>0</v>
       </c>
       <c r="Y14" s="81" t="str">
-        <f>ROUNDUP(AB14*Y13,2)</f>
+        <f>AB14*Y13</f>
         <v>0</v>
       </c>
       <c r="Z14" s="81" t="str">
-        <f>ROUNDUP(AB14*Z13,2)</f>
+        <f>AB14*Z13</f>
         <v>0</v>
       </c>
       <c r="AA14" s="81" t="str">
-        <f>ROUNDUP(AB14*AA13,2)</f>
+        <f>AB14*AA13</f>
         <v>0</v>
       </c>
       <c r="AB14" s="86" t="str">
-        <f>IF(AB7&lt;1, ROUNDUP(AF7*0.6, 0), ROUNDUP(AF7*0.6*AB7, 0))</f>
+        <f>IF(AB7&lt;1, AF7*0.6, AF7*0.6*AB7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:32">
       <c r="B15" s="74" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C15" s="81" t="str">
-        <f>ROUNDUP(C11+C14,2)</f>
+        <f>C11+C14</f>
         <v>0</v>
       </c>
       <c r="D15" s="81" t="str">
-        <f>ROUNDUP(D11+D14,2)</f>
+        <f>D11+D14</f>
         <v>0</v>
       </c>
       <c r="E15" s="81" t="str">
-        <f>ROUNDUP(E11+E14,2)</f>
+        <f>E11+E14</f>
         <v>0</v>
       </c>
       <c r="F15" s="81" t="str">
-        <f>ROUNDUP(F11+F14,2)</f>
+        <f>F11+F14</f>
         <v>0</v>
       </c>
       <c r="G15" s="81" t="str">
-        <f>ROUNDUP(G11+G14,2)</f>
+        <f>G11+G14</f>
         <v>0</v>
       </c>
       <c r="H15" s="81" t="str">
-        <f>ROUNDUP(H11+H14,2)</f>
+        <f>H11+H14</f>
         <v>0</v>
       </c>
       <c r="I15" s="81" t="str">
-        <f>ROUNDUP(I11+I14,2)</f>
+        <f>I11+I14</f>
         <v>0</v>
       </c>
       <c r="J15" s="81" t="str">
-        <f>ROUNDUP(J11+J14,2)</f>
+        <f>J11+J14</f>
         <v>0</v>
       </c>
       <c r="K15" s="81" t="str">
-        <f>ROUNDUP(K11+K14,2)</f>
+        <f>K11+K14</f>
         <v>0</v>
       </c>
       <c r="L15" s="81" t="str">
-        <f>ROUNDUP(L11+L14,2)</f>
+        <f>L11+L14</f>
         <v>0</v>
       </c>
       <c r="M15" s="81" t="str">
-        <f>ROUNDUP(M11+M14,2)</f>
+        <f>M11+M14</f>
         <v>0</v>
       </c>
       <c r="N15" s="81" t="str">
-        <f>ROUNDUP(N11+N14,2)</f>
+        <f>N11+N14</f>
         <v>0</v>
       </c>
       <c r="O15" s="81" t="str">
-        <f>ROUNDUP(O11+O14,2)</f>
+        <f>O11+O14</f>
         <v>0</v>
       </c>
       <c r="P15" s="81" t="str">
-        <f>ROUNDUP(P11+P14,2)</f>
+        <f>P11+P14</f>
         <v>0</v>
       </c>
       <c r="Q15" s="81" t="str">
-        <f>ROUNDUP(Q11+Q14,2)</f>
+        <f>Q11+Q14</f>
         <v>0</v>
       </c>
       <c r="R15" s="81" t="str">
-        <f>ROUNDUP(R11+R14,2)</f>
+        <f>R11+R14</f>
         <v>0</v>
       </c>
       <c r="S15" s="81" t="str">
-        <f>ROUNDUP(S11+S14,2)</f>
+        <f>S11+S14</f>
         <v>0</v>
       </c>
       <c r="T15" s="81" t="str">
-        <f>ROUNDUP(T11+T14,2)</f>
+        <f>T11+T14</f>
         <v>0</v>
       </c>
       <c r="U15" s="81" t="str">
-        <f>ROUNDUP(U11+U14,2)</f>
+        <f>U11+U14</f>
         <v>0</v>
       </c>
       <c r="V15" s="81" t="str">
-        <f>ROUNDUP(V11+V14,2)</f>
+        <f>V11+V14</f>
         <v>0</v>
       </c>
       <c r="W15" s="81" t="str">
-        <f>ROUNDUP(W11+W14,2)</f>
+        <f>W11+W14</f>
         <v>0</v>
       </c>
       <c r="X15" s="81" t="str">
-        <f>ROUNDUP(X11+X14,2)</f>
+        <f>X11+X14</f>
         <v>0</v>
       </c>
       <c r="Y15" s="81" t="str">
-        <f>ROUNDUP(Y11+Y14,2)</f>
+        <f>Y11+Y14</f>
         <v>0</v>
       </c>
       <c r="Z15" s="81" t="str">
-        <f>ROUNDUP(Z11+Z14,2)</f>
+        <f>Z11+Z14</f>
         <v>0</v>
       </c>
       <c r="AA15" s="81" t="str">
-        <f>ROUNDUP(AA11+AA14,2)</f>
+        <f>AA11+AA14</f>
         <v>0</v>
       </c>
       <c r="AB15" s="86" t="str">
@@ -5187,106 +5184,106 @@
     </row>
     <row r="16" spans="1:32">
       <c r="B16" s="79" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C16" s="81" t="str">
-        <f>ROUNDUP(C12+C14,2)</f>
+        <f>C12+C14</f>
         <v>0</v>
       </c>
       <c r="D16" s="81" t="str">
-        <f>ROUNDUP(D12+D14,2)</f>
+        <f>D12+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="81" t="str">
-        <f>ROUNDUP(E12+E14,2)</f>
+        <f>E12+E14</f>
         <v>0</v>
       </c>
       <c r="F16" s="81" t="str">
-        <f>ROUNDUP(F12+F14,2)</f>
+        <f>F12+F14</f>
         <v>0</v>
       </c>
       <c r="G16" s="81" t="str">
-        <f>ROUNDUP(G12+G14,2)</f>
+        <f>G12+G14</f>
         <v>0</v>
       </c>
       <c r="H16" s="81" t="str">
-        <f>ROUNDUP(H12+H14,2)</f>
+        <f>H12+H14</f>
         <v>0</v>
       </c>
       <c r="I16" s="81" t="str">
-        <f>ROUNDUP(I12+I14,2)</f>
+        <f>I12+I14</f>
         <v>0</v>
       </c>
       <c r="J16" s="81" t="str">
-        <f>ROUNDUP(J12+J14,2)</f>
+        <f>J12+J14</f>
         <v>0</v>
       </c>
       <c r="K16" s="81" t="str">
-        <f>ROUNDUP(K12+K14,2)</f>
+        <f>K12+K14</f>
         <v>0</v>
       </c>
       <c r="L16" s="81" t="str">
-        <f>ROUNDUP(L12+L14,2)</f>
+        <f>L12+L14</f>
         <v>0</v>
       </c>
       <c r="M16" s="81" t="str">
-        <f>ROUNDUP(M12+M14,2)</f>
+        <f>M12+M14</f>
         <v>0</v>
       </c>
       <c r="N16" s="81" t="str">
-        <f>ROUNDUP(N12+N14,2)</f>
+        <f>N12+N14</f>
         <v>0</v>
       </c>
       <c r="O16" s="81" t="str">
-        <f>ROUNDUP(O12+O14,2)</f>
+        <f>O12+O14</f>
         <v>0</v>
       </c>
       <c r="P16" s="81" t="str">
-        <f>ROUNDUP(P12+P14,2)</f>
+        <f>P12+P14</f>
         <v>0</v>
       </c>
       <c r="Q16" s="81" t="str">
-        <f>ROUNDUP(Q12+Q14,2)</f>
+        <f>Q12+Q14</f>
         <v>0</v>
       </c>
       <c r="R16" s="81" t="str">
-        <f>ROUNDUP(R12+R14,2)</f>
+        <f>R12+R14</f>
         <v>0</v>
       </c>
       <c r="S16" s="81" t="str">
-        <f>ROUNDUP(S12+S14,2)</f>
+        <f>S12+S14</f>
         <v>0</v>
       </c>
       <c r="T16" s="81" t="str">
-        <f>ROUNDUP(T12+T14,2)</f>
+        <f>T12+T14</f>
         <v>0</v>
       </c>
       <c r="U16" s="81" t="str">
-        <f>ROUNDUP(U12+U14,2)</f>
+        <f>U12+U14</f>
         <v>0</v>
       </c>
       <c r="V16" s="81" t="str">
-        <f>ROUNDUP(V12+V14,2)</f>
+        <f>V12+V14</f>
         <v>0</v>
       </c>
       <c r="W16" s="81" t="str">
-        <f>ROUNDUP(W12+W14,2)</f>
+        <f>W12+W14</f>
         <v>0</v>
       </c>
       <c r="X16" s="81" t="str">
-        <f>ROUNDUP(X12+X14,2)</f>
+        <f>X12+X14</f>
         <v>0</v>
       </c>
       <c r="Y16" s="81" t="str">
-        <f>ROUNDUP(Y12+Y14,2)</f>
+        <f>Y12+Y14</f>
         <v>0</v>
       </c>
       <c r="Z16" s="81" t="str">
-        <f>ROUNDUP(Z12+Z14,2)</f>
+        <f>Z12+Z14</f>
         <v>0</v>
       </c>
       <c r="AA16" s="81" t="str">
-        <f>ROUNDUP(AA12+AA14,2)</f>
+        <f>AA12+AA14</f>
         <v>0</v>
       </c>
       <c r="AB16" s="86" t="str">
@@ -5296,106 +5293,106 @@
     </row>
     <row r="17" spans="1:32">
       <c r="B17" s="74" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*C13,2),ROUND(50*C13,2))</f>
+        <f>IF(AB15&gt;5000,100*C13,50*C13)</f>
         <v>0</v>
       </c>
       <c r="D17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*D13,2),ROUND(50*D13,2))</f>
+        <f>IF(AB15&gt;5000,100*D13,50*D13)</f>
         <v>0</v>
       </c>
       <c r="E17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*E13,2),ROUND(50*E13,2))</f>
+        <f>IF(AB15&gt;5000,100*E13,50*E13)</f>
         <v>0</v>
       </c>
       <c r="F17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*F13,2),ROUND(50*F13,2))</f>
+        <f>IF(AB15&gt;5000,100*F13,50*F13)</f>
         <v>0</v>
       </c>
       <c r="G17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*G13,2),ROUND(50*G13,2))</f>
+        <f>IF(AB15&gt;5000,100*G13,50*G13)</f>
         <v>0</v>
       </c>
       <c r="H17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*H13,2),ROUND(50*H13,2))</f>
+        <f>IF(AB15&gt;5000,100*H13,50*H13)</f>
         <v>0</v>
       </c>
       <c r="I17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*I13,2),ROUND(50*I13,2))</f>
+        <f>IF(AB15&gt;5000,100*I13,50*I13)</f>
         <v>0</v>
       </c>
       <c r="J17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*J13,2),ROUND(50*J13,2))</f>
+        <f>IF(AB15&gt;5000,100*J13,50*J13)</f>
         <v>0</v>
       </c>
       <c r="K17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*K13,2),ROUND(50*K13,2))</f>
+        <f>IF(AB15&gt;5000,100*K13,50*K13)</f>
         <v>0</v>
       </c>
       <c r="L17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*L13,2),ROUND(50*L13,2))</f>
+        <f>IF(AB15&gt;5000,100*L13,50*L13)</f>
         <v>0</v>
       </c>
       <c r="M17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*M13,2),ROUND(50*M13,2))</f>
+        <f>IF(AB15&gt;5000,100*M13,50*M13)</f>
         <v>0</v>
       </c>
       <c r="N17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*N13,2),ROUND(50*N13,2))</f>
+        <f>IF(AB15&gt;5000,100*N13,50*N13)</f>
         <v>0</v>
       </c>
       <c r="O17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*O13,2),ROUND(50*O13,2))</f>
+        <f>IF(AB15&gt;5000,100*O13,50*O13)</f>
         <v>0</v>
       </c>
       <c r="P17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*P13,2),ROUND(50*P13,2))</f>
+        <f>IF(AB15&gt;5000,100*P13,50*P13)</f>
         <v>0</v>
       </c>
       <c r="Q17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*Q13,2),ROUND(50*Q13,2))</f>
+        <f>IF(AB15&gt;5000,100*Q13,50*Q13)</f>
         <v>0</v>
       </c>
       <c r="R17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*R13,2),ROUND(50*R13,2))</f>
+        <f>IF(AB15&gt;5000,100*R13,50*R13)</f>
         <v>0</v>
       </c>
       <c r="S17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*S13,2),ROUND(50*S13,2))</f>
+        <f>IF(AB15&gt;5000,100*S13,50*S13)</f>
         <v>0</v>
       </c>
       <c r="T17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*T13,2),ROUND(50*T13,2))</f>
+        <f>IF(AB15&gt;5000,100*T13,50*T13)</f>
         <v>0</v>
       </c>
       <c r="U17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*U13,2),ROUND(50*U13,2))</f>
+        <f>IF(AB15&gt;5000,100*U13,50*U13)</f>
         <v>0</v>
       </c>
       <c r="V17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*V13,2),ROUND(50*V13,2))</f>
+        <f>IF(AB15&gt;5000,100*V13,50*V13)</f>
         <v>0</v>
       </c>
       <c r="W17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*W13,2),ROUND(50*W13,2))</f>
+        <f>IF(AB15&gt;5000,100*W13,50*W13)</f>
         <v>0</v>
       </c>
       <c r="X17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*X13,2),ROUND(50*X13,2))</f>
+        <f>IF(AB15&gt;5000,100*X13,50*X13)</f>
         <v>0</v>
       </c>
       <c r="Y17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*Y13,2),ROUND(50*Y13,2))</f>
+        <f>IF(AB15&gt;5000,100*Y13,50*Y13)</f>
         <v>0</v>
       </c>
       <c r="Z17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*Z13,2),ROUND(50*Z13,2))</f>
+        <f>IF(AB15&gt;5000,100*Z13,50*Z13)</f>
         <v>0</v>
       </c>
       <c r="AA17" s="81" t="str">
-        <f>IF(AB15&gt;5000,ROUND(100*AA13,2),ROUND(50*AA13,2))</f>
+        <f>IF(AB15&gt;5000,100*AA13,50*AA13)</f>
         <v>0</v>
       </c>
       <c r="AB17" s="86" t="str">
@@ -5405,106 +5402,106 @@
     </row>
     <row r="18" spans="1:32">
       <c r="B18" s="74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C18" s="81" t="str">
-        <f>ROUNDUP(C15+C17,2)</f>
+        <f>C15+C17</f>
         <v>0</v>
       </c>
       <c r="D18" s="81" t="str">
-        <f>ROUNDUP(D15+D17,2)</f>
+        <f>D15+D17</f>
         <v>0</v>
       </c>
       <c r="E18" s="81" t="str">
-        <f>ROUNDUP(E15+E17,2)</f>
+        <f>E15+E17</f>
         <v>0</v>
       </c>
       <c r="F18" s="81" t="str">
-        <f>ROUNDUP(F15+F17,2)</f>
+        <f>F15+F17</f>
         <v>0</v>
       </c>
       <c r="G18" s="81" t="str">
-        <f>ROUNDUP(G15+G17,2)</f>
+        <f>G15+G17</f>
         <v>0</v>
       </c>
       <c r="H18" s="81" t="str">
-        <f>ROUNDUP(H15+H17,2)</f>
+        <f>H15+H17</f>
         <v>0</v>
       </c>
       <c r="I18" s="81" t="str">
-        <f>ROUNDUP(I15+I17,2)</f>
+        <f>I15+I17</f>
         <v>0</v>
       </c>
       <c r="J18" s="81" t="str">
-        <f>ROUNDUP(J15+J17,2)</f>
+        <f>J15+J17</f>
         <v>0</v>
       </c>
       <c r="K18" s="81" t="str">
-        <f>ROUNDUP(K15+K17,2)</f>
+        <f>K15+K17</f>
         <v>0</v>
       </c>
       <c r="L18" s="81" t="str">
-        <f>ROUNDUP(L15+L17,2)</f>
+        <f>L15+L17</f>
         <v>0</v>
       </c>
       <c r="M18" s="81" t="str">
-        <f>ROUNDUP(M15+M17,2)</f>
+        <f>M15+M17</f>
         <v>0</v>
       </c>
       <c r="N18" s="81" t="str">
-        <f>ROUNDUP(N15+N17,2)</f>
+        <f>N15+N17</f>
         <v>0</v>
       </c>
       <c r="O18" s="81" t="str">
-        <f>ROUNDUP(O15+O17,2)</f>
+        <f>O15+O17</f>
         <v>0</v>
       </c>
       <c r="P18" s="81" t="str">
-        <f>ROUNDUP(P15+P17,2)</f>
+        <f>P15+P17</f>
         <v>0</v>
       </c>
       <c r="Q18" s="81" t="str">
-        <f>ROUNDUP(Q15+Q17,2)</f>
+        <f>Q15+Q17</f>
         <v>0</v>
       </c>
       <c r="R18" s="81" t="str">
-        <f>ROUNDUP(R15+R17,2)</f>
+        <f>R15+R17</f>
         <v>0</v>
       </c>
       <c r="S18" s="81" t="str">
-        <f>ROUNDUP(S15+S17,2)</f>
+        <f>S15+S17</f>
         <v>0</v>
       </c>
       <c r="T18" s="81" t="str">
-        <f>ROUNDUP(T15+T17,2)</f>
+        <f>T15+T17</f>
         <v>0</v>
       </c>
       <c r="U18" s="81" t="str">
-        <f>ROUNDUP(U15+U17,2)</f>
+        <f>U15+U17</f>
         <v>0</v>
       </c>
       <c r="V18" s="81" t="str">
-        <f>ROUNDUP(V15+V17,2)</f>
+        <f>V15+V17</f>
         <v>0</v>
       </c>
       <c r="W18" s="81" t="str">
-        <f>ROUNDUP(W15+W17,2)</f>
+        <f>W15+W17</f>
         <v>0</v>
       </c>
       <c r="X18" s="81" t="str">
-        <f>ROUNDUP(X15+X17,2)</f>
+        <f>X15+X17</f>
         <v>0</v>
       </c>
       <c r="Y18" s="81" t="str">
-        <f>ROUNDUP(Y15+Y17,2)</f>
+        <f>Y15+Y17</f>
         <v>0</v>
       </c>
       <c r="Z18" s="81" t="str">
-        <f>ROUNDUP(Z15+Z17,2)</f>
+        <f>Z15+Z17</f>
         <v>0</v>
       </c>
       <c r="AA18" s="81" t="str">
-        <f>ROUNDUP(AA15+AA17,2)</f>
+        <f>AA15+AA17</f>
         <v>0</v>
       </c>
       <c r="AB18" s="86" t="str">
@@ -5514,106 +5511,106 @@
     </row>
     <row r="19" spans="1:32">
       <c r="B19" s="79" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C19" s="81" t="str">
-        <f>ROUNDUP(C16+C17,2)</f>
+        <f>C16+C17</f>
         <v>0</v>
       </c>
       <c r="D19" s="81" t="str">
-        <f>ROUNDUP(D16+D17,2)</f>
+        <f>D16+D17</f>
         <v>0</v>
       </c>
       <c r="E19" s="81" t="str">
-        <f>ROUNDUP(E16+E17,2)</f>
+        <f>E16+E17</f>
         <v>0</v>
       </c>
       <c r="F19" s="81" t="str">
-        <f>ROUNDUP(F16+F17,2)</f>
+        <f>F16+F17</f>
         <v>0</v>
       </c>
       <c r="G19" s="81" t="str">
-        <f>ROUNDUP(G16+G17,2)</f>
+        <f>G16+G17</f>
         <v>0</v>
       </c>
       <c r="H19" s="81" t="str">
-        <f>ROUNDUP(H16+H17,2)</f>
+        <f>H16+H17</f>
         <v>0</v>
       </c>
       <c r="I19" s="81" t="str">
-        <f>ROUNDUP(I16+I17,2)</f>
+        <f>I16+I17</f>
         <v>0</v>
       </c>
       <c r="J19" s="81" t="str">
-        <f>ROUNDUP(J16+J17,2)</f>
+        <f>J16+J17</f>
         <v>0</v>
       </c>
       <c r="K19" s="81" t="str">
-        <f>ROUNDUP(K16+K17,2)</f>
+        <f>K16+K17</f>
         <v>0</v>
       </c>
       <c r="L19" s="81" t="str">
-        <f>ROUNDUP(L16+L17,2)</f>
+        <f>L16+L17</f>
         <v>0</v>
       </c>
       <c r="M19" s="81" t="str">
-        <f>ROUNDUP(M16+M17,2)</f>
+        <f>M16+M17</f>
         <v>0</v>
       </c>
       <c r="N19" s="81" t="str">
-        <f>ROUNDUP(N16+N17,2)</f>
+        <f>N16+N17</f>
         <v>0</v>
       </c>
       <c r="O19" s="81" t="str">
-        <f>ROUNDUP(O16+O17,2)</f>
+        <f>O16+O17</f>
         <v>0</v>
       </c>
       <c r="P19" s="81" t="str">
-        <f>ROUNDUP(P16+P17,2)</f>
+        <f>P16+P17</f>
         <v>0</v>
       </c>
       <c r="Q19" s="81" t="str">
-        <f>ROUNDUP(Q16+Q17,2)</f>
+        <f>Q16+Q17</f>
         <v>0</v>
       </c>
       <c r="R19" s="81" t="str">
-        <f>ROUNDUP(R16+R17,2)</f>
+        <f>R16+R17</f>
         <v>0</v>
       </c>
       <c r="S19" s="81" t="str">
-        <f>ROUNDUP(S16+S17,2)</f>
+        <f>S16+S17</f>
         <v>0</v>
       </c>
       <c r="T19" s="81" t="str">
-        <f>ROUNDUP(T16+T17,2)</f>
+        <f>T16+T17</f>
         <v>0</v>
       </c>
       <c r="U19" s="81" t="str">
-        <f>ROUNDUP(U16+U17,2)</f>
+        <f>U16+U17</f>
         <v>0</v>
       </c>
       <c r="V19" s="81" t="str">
-        <f>ROUNDUP(V16+V17,2)</f>
+        <f>V16+V17</f>
         <v>0</v>
       </c>
       <c r="W19" s="81" t="str">
-        <f>ROUNDUP(W16+W17,2)</f>
+        <f>W16+W17</f>
         <v>0</v>
       </c>
       <c r="X19" s="81" t="str">
-        <f>ROUNDUP(X16+X17,2)</f>
+        <f>X16+X17</f>
         <v>0</v>
       </c>
       <c r="Y19" s="81" t="str">
-        <f>ROUNDUP(Y16+Y17,2)</f>
+        <f>Y16+Y17</f>
         <v>0</v>
       </c>
       <c r="Z19" s="81" t="str">
-        <f>ROUNDUP(Z16+Z17,2)</f>
+        <f>Z16+Z17</f>
         <v>0</v>
       </c>
       <c r="AA19" s="81" t="str">
-        <f>ROUNDUP(AA16+AA17,2)</f>
+        <f>AA16+AA17</f>
         <v>0</v>
       </c>
       <c r="AB19" s="86" t="str">
@@ -5623,7 +5620,7 @@
     </row>
     <row r="23" spans="1:32">
       <c r="B23" s="75" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C23" s="74"/>
       <c r="D23" s="74"/>
@@ -5631,7 +5628,7 @@
     </row>
     <row r="26" spans="1:32">
       <c r="B26" s="74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="81">
         <v>0</v>
@@ -5796,7 +5793,7 @@
     </row>
     <row r="28" spans="1:32">
       <c r="B28" s="74" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C28" s="81" t="str">
         <f>MAX(C19,C18)*C27</f>
@@ -5905,7 +5902,7 @@
     </row>
     <row r="29" spans="1:32">
       <c r="B29" s="74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="81" t="str">
         <f>0.16*(MAX(C19,C18)+C28)</f>
@@ -6014,7 +6011,7 @@
     </row>
     <row r="30" spans="1:32">
       <c r="B30" s="74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" s="81" t="str">
         <f>0.02*(MAX(C19,C18)+C28)</f>
@@ -6123,7 +6120,7 @@
     </row>
     <row r="31" spans="1:32">
       <c r="B31" s="74" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C31" s="81" t="str">
         <f>0.035*(MAX(C18,C19) +C28+C29+C30)</f>
@@ -6232,7 +6229,7 @@
     </row>
     <row r="32" spans="1:32">
       <c r="B32" s="74" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" s="81" t="str">
         <f>SUM(C28:C31)</f>
@@ -6341,7 +6338,7 @@
     </row>
     <row r="37" spans="1:32">
       <c r="B37" s="75" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C37" s="74"/>
       <c r="D37" s="74"/>
@@ -6349,7 +6346,7 @@
     </row>
     <row r="40" spans="1:32">
       <c r="B40" s="74" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C40" s="81" t="str">
         <f>C13*AB40</f>
@@ -6452,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="AB40" s="81" t="str">
-        <f>IF(AB7&lt;1, ROUNDUP(AF7*0.4, 0), ROUNDUP(AF7*0.4*AB7, 0))</f>
+        <f>IF(AB7&lt;1, AF7*0.4,AF7*0.4*AB7)</f>
         <v>0</v>
       </c>
     </row>
@@ -6461,189 +6458,189 @@
     </row>
     <row r="43" spans="1:32">
       <c r="B43" s="74" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C43" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="74" t="s">
+      <c r="E43" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="E43" s="74" t="s">
+      <c r="F43" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="F43" s="74" t="s">
+      <c r="G43" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="G43" s="74" t="s">
+      <c r="H43" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="H43" s="74" t="s">
+      <c r="I43" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="I43" s="74" t="s">
+      <c r="J43" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="J43" s="74" t="s">
+      <c r="K43" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="K43" s="74" t="s">
+      <c r="L43" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="L43" s="74" t="s">
+      <c r="M43" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="M43" s="74" t="s">
+      <c r="N43" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="N43" s="74" t="s">
+      <c r="O43" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="O43" s="74" t="s">
+      <c r="P43" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="P43" s="74" t="s">
+      <c r="Q43" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="Q43" s="74" t="s">
+      <c r="R43" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="R43" s="74" t="s">
+      <c r="S43" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="S43" s="74" t="s">
+      <c r="T43" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="T43" s="74" t="s">
+      <c r="U43" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="U43" s="74" t="s">
+      <c r="V43" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="V43" s="74" t="s">
+      <c r="W43" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="W43" s="74" t="s">
+      <c r="X43" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="X43" s="74" t="s">
+      <c r="Y43" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="Y43" s="74" t="s">
+      <c r="Z43" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="Z43" s="74" t="s">
+      <c r="AA43" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="AA43" s="74" t="s">
-        <v>75</v>
-      </c>
       <c r="AB43" s="74" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:32">
       <c r="B44" s="74" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C44" s="81" t="str">
-        <f>SUM(C15,C40,C32,(C26*C10))</f>
+        <f>SUM(C15,C40,C32,(C26))</f>
         <v>0</v>
       </c>
       <c r="D44" s="81" t="str">
-        <f>SUM(D15,D40,D32,(D26*D10))</f>
+        <f>SUM(D15,D40,D32,(D26))</f>
         <v>0</v>
       </c>
       <c r="E44" s="81" t="str">
-        <f>SUM(E15,E40,E32,(E26*E10))</f>
+        <f>SUM(E15,E40,E32,(E26))</f>
         <v>0</v>
       </c>
       <c r="F44" s="81" t="str">
-        <f>SUM(F15,F40,F32,(F26*F10))</f>
+        <f>SUM(F15,F40,F32,(F26))</f>
         <v>0</v>
       </c>
       <c r="G44" s="81" t="str">
-        <f>SUM(G15,G40,G32,(G26*G10))</f>
+        <f>SUM(G15,G40,G32,(G26))</f>
         <v>0</v>
       </c>
       <c r="H44" s="81" t="str">
-        <f>SUM(H15,H40,H32,(H26*H10))</f>
+        <f>SUM(H15,H40,H32,(H26))</f>
         <v>0</v>
       </c>
       <c r="I44" s="81" t="str">
-        <f>SUM(I15,I40,I32,(I26*I10))</f>
+        <f>SUM(I15,I40,I32,(I26))</f>
         <v>0</v>
       </c>
       <c r="J44" s="81" t="str">
-        <f>SUM(J15,J40,J32,(J26*J10))</f>
+        <f>SUM(J15,J40,J32,(J26))</f>
         <v>0</v>
       </c>
       <c r="K44" s="81" t="str">
-        <f>SUM(K15,K40,K32,(K26*K10))</f>
+        <f>SUM(K15,K40,K32,(K26))</f>
         <v>0</v>
       </c>
       <c r="L44" s="81" t="str">
-        <f>SUM(L15,L40,L32,(L26*L10))</f>
+        <f>SUM(L15,L40,L32,(L26))</f>
         <v>0</v>
       </c>
       <c r="M44" s="81" t="str">
-        <f>SUM(M15,M40,M32,(M26*M10))</f>
+        <f>SUM(M15,M40,M32,(M26))</f>
         <v>0</v>
       </c>
       <c r="N44" s="81" t="str">
-        <f>SUM(N15,N40,N32,(N26*N10))</f>
+        <f>SUM(N15,N40,N32,(N26))</f>
         <v>0</v>
       </c>
       <c r="O44" s="81" t="str">
-        <f>SUM(O15,O40,O32,(O26*O10))</f>
+        <f>SUM(O15,O40,O32,(O26))</f>
         <v>0</v>
       </c>
       <c r="P44" s="81" t="str">
-        <f>SUM(P15,P40,P32,(P26*P10))</f>
+        <f>SUM(P15,P40,P32,(P26))</f>
         <v>0</v>
       </c>
       <c r="Q44" s="81" t="str">
-        <f>SUM(Q15,Q40,Q32,(Q26*Q10))</f>
+        <f>SUM(Q15,Q40,Q32,(Q26))</f>
         <v>0</v>
       </c>
       <c r="R44" s="81" t="str">
-        <f>SUM(R15,R40,R32,(R26*R10))</f>
+        <f>SUM(R15,R40,R32,(R26))</f>
         <v>0</v>
       </c>
       <c r="S44" s="81" t="str">
-        <f>SUM(S15,S40,S32,(S26*S10))</f>
+        <f>SUM(S15,S40,S32,(S26))</f>
         <v>0</v>
       </c>
       <c r="T44" s="81" t="str">
-        <f>SUM(T15,T40,T32,(T26*T10))</f>
+        <f>SUM(T15,T40,T32,(T26))</f>
         <v>0</v>
       </c>
       <c r="U44" s="81" t="str">
-        <f>SUM(U15,U40,U32,(U26*U10))</f>
+        <f>SUM(U15,U40,U32,(U26))</f>
         <v>0</v>
       </c>
       <c r="V44" s="81" t="str">
-        <f>SUM(V15,V40,V32,(V26*V10))</f>
+        <f>SUM(V15,V40,V32,(V26))</f>
         <v>0</v>
       </c>
       <c r="W44" s="81" t="str">
-        <f>SUM(W15,W40,W32,(W26*W10))</f>
+        <f>SUM(W15,W40,W32,(W26))</f>
         <v>0</v>
       </c>
       <c r="X44" s="81" t="str">
-        <f>SUM(X15,X40,X32,(X26*X10))</f>
+        <f>SUM(X15,X40,X32,(X26))</f>
         <v>0</v>
       </c>
       <c r="Y44" s="81" t="str">
-        <f>SUM(Y15,Y40,Y32,(Y26*Y10))</f>
+        <f>SUM(Y15,Y40,Y32,(Y26))</f>
         <v>0</v>
       </c>
       <c r="Z44" s="81" t="str">
-        <f>SUM(Z15,Z40,Z32,(Z26*Z10))</f>
+        <f>SUM(Z15,Z40,Z32,(Z26))</f>
         <v>0</v>
       </c>
       <c r="AA44" s="81" t="str">
-        <f>SUM(AA15,AA40,AA32,(AA26*AA10))</f>
+        <f>SUM(AA15,AA40,AA32,(AA26))</f>
         <v>0</v>
       </c>
       <c r="AB44" s="81" t="str">
@@ -6653,7 +6650,7 @@
     </row>
     <row r="45" spans="1:32">
       <c r="B45" s="74" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C45" s="74">
         <v>65</v>
@@ -6734,212 +6731,212 @@
     </row>
     <row r="46" spans="1:32">
       <c r="B46" s="74" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="81" t="str">
-        <f>ROUND(SUM(C44/C45),2)</f>
+        <f>SUM(C44/C45)</f>
         <v>0</v>
       </c>
       <c r="D46" s="81" t="str">
-        <f>ROUND(SUM(D44/D45),2)</f>
+        <f>SUM(D44/D45)</f>
         <v>0</v>
       </c>
       <c r="E46" s="81" t="str">
-        <f>ROUND(SUM(E44/E45),2)</f>
+        <f>SUM(E44/E45)</f>
         <v>0</v>
       </c>
       <c r="F46" s="81" t="str">
-        <f>ROUND(SUM(F44/F45),2)</f>
+        <f>SUM(F44/F45)</f>
         <v>0</v>
       </c>
       <c r="G46" s="81" t="str">
-        <f>ROUND(SUM(G44/G45),2)</f>
+        <f>SUM(G44/G45)</f>
         <v>0</v>
       </c>
       <c r="H46" s="81" t="str">
-        <f>ROUND(SUM(H44/H45),2)</f>
+        <f>SUM(H44/H45)</f>
         <v>0</v>
       </c>
       <c r="I46" s="81" t="str">
-        <f>ROUND(SUM(I44/I45),2)</f>
+        <f>SUM(I44/I45)</f>
         <v>0</v>
       </c>
       <c r="J46" s="81" t="str">
-        <f>ROUND(SUM(J44/J45),2)</f>
+        <f>SUM(J44/J45)</f>
         <v>0</v>
       </c>
       <c r="K46" s="81" t="str">
-        <f>ROUND(SUM(K44/K45),2)</f>
+        <f>SUM(K44/K45)</f>
         <v>0</v>
       </c>
       <c r="L46" s="81" t="str">
-        <f>ROUND(SUM(L44/L45),2)</f>
+        <f>SUM(L44/L45)</f>
         <v>0</v>
       </c>
       <c r="M46" s="81" t="str">
-        <f>ROUND(SUM(M44/M45),2)</f>
+        <f>SUM(M44/M45)</f>
         <v>0</v>
       </c>
       <c r="N46" s="81" t="str">
-        <f>ROUND(SUM(N44/N45),2)</f>
+        <f>SUM(N44/N45)</f>
         <v>0</v>
       </c>
       <c r="O46" s="81" t="str">
-        <f>ROUND(SUM(O44/O45),2)</f>
+        <f>SUM(O44/O45)</f>
         <v>0</v>
       </c>
       <c r="P46" s="81" t="str">
-        <f>ROUND(SUM(P44/P45),2)</f>
+        <f>SUM(P44/P45)</f>
         <v>0</v>
       </c>
       <c r="Q46" s="81" t="str">
-        <f>ROUND(SUM(Q44/Q45),2)</f>
+        <f>SUM(Q44/Q45)</f>
         <v>0</v>
       </c>
       <c r="R46" s="81" t="str">
-        <f>ROUND(SUM(R44/R45),2)</f>
+        <f>SUM(R44/R45)</f>
         <v>0</v>
       </c>
       <c r="S46" s="81" t="str">
-        <f>ROUND(SUM(S44/S45),2)</f>
+        <f>SUM(S44/S45)</f>
         <v>0</v>
       </c>
       <c r="T46" s="81" t="str">
-        <f>ROUND(SUM(T44/T45),2)</f>
+        <f>SUM(T44/T45)</f>
         <v>0</v>
       </c>
       <c r="U46" s="81" t="str">
-        <f>ROUND(SUM(U44/U45),2)</f>
+        <f>SUM(U44/U45)</f>
         <v>0</v>
       </c>
       <c r="V46" s="81" t="str">
-        <f>ROUND(SUM(V44/V45),2)</f>
+        <f>SUM(V44/V45)</f>
         <v>0</v>
       </c>
       <c r="W46" s="81" t="str">
-        <f>ROUND(SUM(W44/W45),2)</f>
+        <f>SUM(W44/W45)</f>
         <v>0</v>
       </c>
       <c r="X46" s="81" t="str">
-        <f>ROUND(SUM(X44/X45),2)</f>
+        <f>SUM(X44/X45)</f>
         <v>0</v>
       </c>
       <c r="Y46" s="81" t="str">
-        <f>ROUND(SUM(Y44/Y45),2)</f>
+        <f>SUM(Y44/Y45)</f>
         <v>0</v>
       </c>
       <c r="Z46" s="81" t="str">
-        <f>ROUND(SUM(Z44/Z45),2)</f>
+        <f>SUM(Z44/Z45)</f>
         <v>0</v>
       </c>
       <c r="AA46" s="81" t="str">
-        <f>ROUND(SUM(AA44/AA45),2)</f>
+        <f>SUM(AA44/AA45)</f>
         <v>0</v>
       </c>
       <c r="AB46" s="74"/>
     </row>
     <row r="47" spans="1:32">
       <c r="B47" s="74" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C47" s="85" t="str">
-        <f>ROUND(C46*3.7,2)</f>
+        <f>C46*3.7</f>
         <v>0</v>
       </c>
       <c r="D47" s="85" t="str">
-        <f>ROUND(D46*3.7,2)</f>
+        <f>D46*3.7</f>
         <v>0</v>
       </c>
       <c r="E47" s="85" t="str">
-        <f>ROUND(E46*3.7,2)</f>
+        <f>E46*3.7</f>
         <v>0</v>
       </c>
       <c r="F47" s="85" t="str">
-        <f>ROUND(F46*3.7,2)</f>
+        <f>F46*3.7</f>
         <v>0</v>
       </c>
       <c r="G47" s="85" t="str">
-        <f>ROUND(G46*3.7,2)</f>
+        <f>G46*3.7</f>
         <v>0</v>
       </c>
       <c r="H47" s="85" t="str">
-        <f>ROUND(H46*3.7,2)</f>
+        <f>H46*3.7</f>
         <v>0</v>
       </c>
       <c r="I47" s="85" t="str">
-        <f>ROUND(I46*3.7,2)</f>
+        <f>I46*3.7</f>
         <v>0</v>
       </c>
       <c r="J47" s="85" t="str">
-        <f>ROUND(J46*3.7,2)</f>
+        <f>J46*3.7</f>
         <v>0</v>
       </c>
       <c r="K47" s="85" t="str">
-        <f>ROUND(K46*3.7,2)</f>
+        <f>K46*3.7</f>
         <v>0</v>
       </c>
       <c r="L47" s="85" t="str">
-        <f>ROUND(L46*3.7,2)</f>
+        <f>L46*3.7</f>
         <v>0</v>
       </c>
       <c r="M47" s="85" t="str">
-        <f>ROUND(M46*3.7,2)</f>
+        <f>M46*3.7</f>
         <v>0</v>
       </c>
       <c r="N47" s="85" t="str">
-        <f>ROUND(N46*3.7,2)</f>
+        <f>N46*3.7</f>
         <v>0</v>
       </c>
       <c r="O47" s="85" t="str">
-        <f>ROUND(O46*3.7,2)</f>
+        <f>O46*3.7</f>
         <v>0</v>
       </c>
       <c r="P47" s="85" t="str">
-        <f>ROUND(P46*3.7,2)</f>
+        <f>P46*3.7</f>
         <v>0</v>
       </c>
       <c r="Q47" s="85" t="str">
-        <f>ROUND(Q46*3.7,2)</f>
+        <f>Q46*3.7</f>
         <v>0</v>
       </c>
       <c r="R47" s="85" t="str">
-        <f>ROUND(R46*3.7,2)</f>
+        <f>R46*3.7</f>
         <v>0</v>
       </c>
       <c r="S47" s="85" t="str">
-        <f>ROUND(S46*3.7,2)</f>
+        <f>S46*3.7</f>
         <v>0</v>
       </c>
       <c r="T47" s="85" t="str">
-        <f>ROUND(T46*3.7,2)</f>
+        <f>T46*3.7</f>
         <v>0</v>
       </c>
       <c r="U47" s="85" t="str">
-        <f>ROUND(U46*3.7,2)</f>
+        <f>U46*3.7</f>
         <v>0</v>
       </c>
       <c r="V47" s="85" t="str">
-        <f>ROUND(V46*3.7,2)</f>
+        <f>V46*3.7</f>
         <v>0</v>
       </c>
       <c r="W47" s="85" t="str">
-        <f>ROUND(W46*3.7,2)</f>
+        <f>W46*3.7</f>
         <v>0</v>
       </c>
       <c r="X47" s="85" t="str">
-        <f>ROUND(X46*3.7,2)</f>
+        <f>X46*3.7</f>
         <v>0</v>
       </c>
       <c r="Y47" s="85" t="str">
-        <f>ROUND(Y46*3.7,2)</f>
+        <f>Y46*3.7</f>
         <v>0</v>
       </c>
       <c r="Z47" s="85" t="str">
-        <f>ROUND(Z46*3.7,2)</f>
+        <f>Z46*3.7</f>
         <v>0</v>
       </c>
       <c r="AA47" s="85" t="str">
-        <f>ROUND(AA46*3.7,2)</f>
+        <f>AA46*3.7</f>
         <v>0</v>
       </c>
       <c r="AB47" s="74"/>
